--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/90.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/90.xlsx
@@ -426,13 +426,13 @@
         <v>-10.43266258492304</v>
       </c>
       <c r="E2">
-        <v>-5.822166010415219</v>
+        <v>-5.103352274229688</v>
       </c>
       <c r="F2">
-        <v>-5.898710817066271</v>
+        <v>-5.937849520113742</v>
       </c>
       <c r="G2">
-        <v>-6.900114938897102</v>
+        <v>-7.791767342807785</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.61899616330591</v>
       </c>
       <c r="E3">
-        <v>-6.516498816115285</v>
+        <v>-5.656632171538837</v>
       </c>
       <c r="F3">
-        <v>-5.936505908186401</v>
+        <v>-5.946322061909576</v>
       </c>
       <c r="G3">
-        <v>-6.934703518691407</v>
+        <v>-7.721894968655928</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.89843667835569</v>
       </c>
       <c r="E4">
-        <v>-6.418348670473037</v>
+        <v>-6.373353752732824</v>
       </c>
       <c r="F4">
-        <v>-5.814644779560566</v>
+        <v>-5.987612035102116</v>
       </c>
       <c r="G4">
-        <v>-6.694728693640717</v>
+        <v>-8.101713858376511</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.19985143971896</v>
       </c>
       <c r="E5">
-        <v>-7.768830189040491</v>
+        <v>-7.017601635908056</v>
       </c>
       <c r="F5">
-        <v>-5.925516786220863</v>
+        <v>-6.032298314646136</v>
       </c>
       <c r="G5">
-        <v>-7.412488072010103</v>
+        <v>-7.674838874360727</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.48842710736376</v>
       </c>
       <c r="E6">
-        <v>-9.487585327807729</v>
+        <v>-8.15719664841231</v>
       </c>
       <c r="F6">
-        <v>-5.56952423813297</v>
+        <v>-5.834174369448967</v>
       </c>
       <c r="G6">
-        <v>-7.780501556337645</v>
+        <v>-7.351838877730655</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.71018160600771</v>
       </c>
       <c r="E7">
-        <v>-9.298992499284291</v>
+        <v>-8.852448734335931</v>
       </c>
       <c r="F7">
-        <v>-5.437395495549435</v>
+        <v>-5.646565720062935</v>
       </c>
       <c r="G7">
-        <v>-7.196259790112605</v>
+        <v>-7.792204334818969</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.837913527685</v>
       </c>
       <c r="E8">
-        <v>-10.98761064353048</v>
+        <v>-9.271903167770406</v>
       </c>
       <c r="F8">
-        <v>-5.625781153559292</v>
+        <v>-5.828257341090771</v>
       </c>
       <c r="G8">
-        <v>-8.265708352755388</v>
+        <v>-7.857829279043941</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.85665195343137</v>
       </c>
       <c r="E9">
-        <v>-10.966661922771</v>
+        <v>-10.0111810779966</v>
       </c>
       <c r="F9">
-        <v>-5.546023454915548</v>
+        <v>-5.521379524682263</v>
       </c>
       <c r="G9">
-        <v>-6.883012660641226</v>
+        <v>-7.914320428126065</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.75453670367111</v>
       </c>
       <c r="E10">
-        <v>-12.14911894175785</v>
+        <v>-10.79587505404572</v>
       </c>
       <c r="F10">
-        <v>-5.492535771716784</v>
+        <v>-5.435280673570087</v>
       </c>
       <c r="G10">
-        <v>-6.865953419477362</v>
+        <v>-7.739718945839363</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.53930575632639</v>
       </c>
       <c r="E11">
-        <v>-12.22715360585803</v>
+        <v>-11.12761294595162</v>
       </c>
       <c r="F11">
-        <v>-4.930700550972436</v>
+        <v>-5.173828868796299</v>
       </c>
       <c r="G11">
-        <v>-7.107474269294891</v>
+        <v>-7.584705961508529</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.23487837356244</v>
       </c>
       <c r="E12">
-        <v>-13.14706328730218</v>
+        <v>-12.20913933625551</v>
       </c>
       <c r="F12">
-        <v>-4.996680014605416</v>
+        <v>-5.076992719409037</v>
       </c>
       <c r="G12">
-        <v>-6.195101160853909</v>
+        <v>-7.507093531885856</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.86171916969695</v>
       </c>
       <c r="E13">
-        <v>-14.12585218779405</v>
+        <v>-13.7691669325799</v>
       </c>
       <c r="F13">
-        <v>-4.94409690861051</v>
+        <v>-4.816623590830708</v>
       </c>
       <c r="G13">
-        <v>-6.729254373069776</v>
+        <v>-7.755927376799636</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.45416304834196</v>
       </c>
       <c r="E14">
-        <v>-15.12282743990074</v>
+        <v>-14.23695829757225</v>
       </c>
       <c r="F14">
-        <v>-4.907843409226989</v>
+        <v>-4.784164014152009</v>
       </c>
       <c r="G14">
-        <v>-6.462450886968833</v>
+        <v>-7.059914972077721</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.04780334325733</v>
       </c>
       <c r="E15">
-        <v>-16.12281412722252</v>
+        <v>-15.29787107419323</v>
       </c>
       <c r="F15">
-        <v>-4.676675888332148</v>
+        <v>-4.610741156538919</v>
       </c>
       <c r="G15">
-        <v>-5.480566253839774</v>
+        <v>-6.764766595069538</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.663824178996492</v>
       </c>
       <c r="E16">
-        <v>-16.04443982757177</v>
+        <v>-15.83459034205633</v>
       </c>
       <c r="F16">
-        <v>-4.267744864633547</v>
+        <v>-3.932936156137445</v>
       </c>
       <c r="G16">
-        <v>-5.741685533249789</v>
+        <v>-6.527036319894474</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.332172991585191</v>
       </c>
       <c r="E17">
-        <v>-18.17788544511741</v>
+        <v>-17.09749570178944</v>
       </c>
       <c r="F17">
-        <v>-4.18934486016299</v>
+        <v>-3.956674680799471</v>
       </c>
       <c r="G17">
-        <v>-5.851208311325497</v>
+        <v>-5.914284135485231</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.082291328894263</v>
       </c>
       <c r="E18">
-        <v>-18.76065929363852</v>
+        <v>-17.540022710293</v>
       </c>
       <c r="F18">
-        <v>-3.831978050553853</v>
+        <v>-3.514896404477661</v>
       </c>
       <c r="G18">
-        <v>-5.453479370237456</v>
+        <v>-6.111149036523531</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.927524650851305</v>
       </c>
       <c r="E19">
-        <v>-19.43781106895348</v>
+        <v>-18.52270609843147</v>
       </c>
       <c r="F19">
-        <v>-3.621300197367257</v>
+        <v>-3.246346319429283</v>
       </c>
       <c r="G19">
-        <v>-5.293401251231538</v>
+        <v>-5.814150064558896</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.891298176268149</v>
       </c>
       <c r="E20">
-        <v>-19.23812347911125</v>
+        <v>-19.41448037086597</v>
       </c>
       <c r="F20">
-        <v>-3.324919452687025</v>
+        <v>-2.765821986208929</v>
       </c>
       <c r="G20">
-        <v>-4.692047275114005</v>
+        <v>-6.604807655703033</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.989988901712614</v>
       </c>
       <c r="E21">
-        <v>-20.311294834871</v>
+        <v>-20.12766068538595</v>
       </c>
       <c r="F21">
-        <v>-2.710677568204567</v>
+        <v>-2.632346318228442</v>
       </c>
       <c r="G21">
-        <v>-4.390443334304243</v>
+        <v>-5.834824421451644</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.210207417176806</v>
       </c>
       <c r="E22">
-        <v>-21.68611237275567</v>
+        <v>-20.15522550667065</v>
       </c>
       <c r="F22">
-        <v>-2.822629765958114</v>
+        <v>-2.333376925414461</v>
       </c>
       <c r="G22">
-        <v>-5.614087176529659</v>
+        <v>-5.78523907036444</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.532171363583323</v>
       </c>
       <c r="E23">
-        <v>-21.54753201117294</v>
+        <v>-21.3233951901633</v>
       </c>
       <c r="F23">
-        <v>-2.594651459564051</v>
+        <v>-1.847772214912738</v>
       </c>
       <c r="G23">
-        <v>-4.626819596353745</v>
+        <v>-6.537454606706561</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.920724438964509</v>
       </c>
       <c r="E24">
-        <v>-22.82928487972598</v>
+        <v>-21.7159414310442</v>
       </c>
       <c r="F24">
-        <v>-2.438711295987044</v>
+        <v>-1.825660603829811</v>
       </c>
       <c r="G24">
-        <v>-5.072445510303961</v>
+        <v>-5.498261119747178</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.32125555664964</v>
       </c>
       <c r="E25">
-        <v>-21.49085815896695</v>
+        <v>-22.52151620074268</v>
       </c>
       <c r="F25">
-        <v>-2.111945206604723</v>
+        <v>-1.864356130316784</v>
       </c>
       <c r="G25">
-        <v>-5.24642461002928</v>
+        <v>-5.845259260991427</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.68645819950573</v>
       </c>
       <c r="E26">
-        <v>-22.58085279566519</v>
+        <v>-22.7348933675101</v>
       </c>
       <c r="F26">
-        <v>-1.700524110493306</v>
+        <v>-1.489833831795669</v>
       </c>
       <c r="G26">
-        <v>-5.018599487107715</v>
+        <v>-6.02094660221501</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.96980541883331</v>
       </c>
       <c r="E27">
-        <v>-22.71619982680644</v>
+        <v>-22.07999904194284</v>
       </c>
       <c r="F27">
-        <v>-1.739811091305879</v>
+        <v>-1.592242408701563</v>
       </c>
       <c r="G27">
-        <v>-6.368169860555929</v>
+        <v>-5.986652660973699</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.12399932784514</v>
       </c>
       <c r="E28">
-        <v>-23.24025748134409</v>
+        <v>-21.87341005771292</v>
       </c>
       <c r="F28">
-        <v>-1.992126003626788</v>
+        <v>-1.586221834418017</v>
       </c>
       <c r="G28">
-        <v>-5.692143219254596</v>
+        <v>-6.295980104526581</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.12083172817187</v>
       </c>
       <c r="E29">
-        <v>-22.12212290716219</v>
+        <v>-21.83103259794914</v>
       </c>
       <c r="F29">
-        <v>-1.990779078229836</v>
+        <v>-1.717940535137166</v>
       </c>
       <c r="G29">
-        <v>-5.49443743964932</v>
+        <v>-6.233695500750733</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.94229741456908</v>
       </c>
       <c r="E30">
-        <v>-22.42745073865535</v>
+        <v>-21.4269523337707</v>
       </c>
       <c r="F30">
-        <v>-2.069744029269102</v>
+        <v>-1.680859496718249</v>
       </c>
       <c r="G30">
-        <v>-5.996349248858224</v>
+        <v>-6.318034958909205</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.57924640934091</v>
       </c>
       <c r="E31">
-        <v>-22.40828623665489</v>
+        <v>-21.1114490211823</v>
       </c>
       <c r="F31">
-        <v>-2.178484646601996</v>
+        <v>-2.040267403607884</v>
       </c>
       <c r="G31">
-        <v>-5.274137186738519</v>
+        <v>-5.922259239689335</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.04662280143358</v>
       </c>
       <c r="E32">
-        <v>-21.10292190462586</v>
+        <v>-21.14837419824084</v>
       </c>
       <c r="F32">
-        <v>-2.105760615575422</v>
+        <v>-2.059169919372366</v>
       </c>
       <c r="G32">
-        <v>-4.876166575826112</v>
+        <v>-6.50393533312144</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.371152092725078</v>
       </c>
       <c r="E33">
-        <v>-21.30345631910753</v>
+        <v>-21.37180457730529</v>
       </c>
       <c r="F33">
-        <v>-2.15979999146445</v>
+        <v>-2.021216610078302</v>
       </c>
       <c r="G33">
-        <v>-5.358261459436939</v>
+        <v>-6.661838423708057</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.586040822394066</v>
       </c>
       <c r="E34">
-        <v>-20.50064844702773</v>
+        <v>-20.04868862716619</v>
       </c>
       <c r="F34">
-        <v>-2.195153055481128</v>
+        <v>-2.095667787139713</v>
       </c>
       <c r="G34">
-        <v>-5.700611594744051</v>
+        <v>-5.864149233838508</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.740991638043978</v>
       </c>
       <c r="E35">
-        <v>-21.56537419876316</v>
+        <v>-19.90659416975351</v>
       </c>
       <c r="F35">
-        <v>-2.266593945400766</v>
+        <v>-1.984808205990457</v>
       </c>
       <c r="G35">
-        <v>-5.136974663955435</v>
+        <v>-6.161879836367323</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.885567056146067</v>
       </c>
       <c r="E36">
-        <v>-18.54853651417123</v>
+        <v>-19.54759033584743</v>
       </c>
       <c r="F36">
-        <v>-2.456191504920919</v>
+        <v>-2.185558075854501</v>
       </c>
       <c r="G36">
-        <v>-4.964485309722789</v>
+        <v>-5.584355167041465</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.061453610397277</v>
       </c>
       <c r="E37">
-        <v>-19.4954404291751</v>
+        <v>-18.95729469199958</v>
       </c>
       <c r="F37">
-        <v>-2.436066318869905</v>
+        <v>-2.002842592716806</v>
       </c>
       <c r="G37">
-        <v>-5.23783705490041</v>
+        <v>-5.165187133041104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.313348555208476</v>
       </c>
       <c r="E38">
-        <v>-18.74810636368926</v>
+        <v>-19.08003445150348</v>
       </c>
       <c r="F38">
-        <v>-2.446483867327512</v>
+        <v>-2.240490431803747</v>
       </c>
       <c r="G38">
-        <v>-4.086194267608603</v>
+        <v>-5.226829490982333</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.674711666152263</v>
       </c>
       <c r="E39">
-        <v>-19.36002547092373</v>
+        <v>-18.41351553315852</v>
       </c>
       <c r="F39">
-        <v>-2.137982450809517</v>
+        <v>-2.398804696357178</v>
       </c>
       <c r="G39">
-        <v>-4.989208463810066</v>
+        <v>-4.989327643449479</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.164169888738657</v>
       </c>
       <c r="E40">
-        <v>-18.73333900995025</v>
+        <v>-17.78443350943498</v>
       </c>
       <c r="F40">
-        <v>-2.272640199073799</v>
+        <v>-2.589626582898669</v>
       </c>
       <c r="G40">
-        <v>-3.647205997464626</v>
+        <v>-4.944274429205538</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.798645372917399</v>
       </c>
       <c r="E41">
-        <v>-18.14898925247447</v>
+        <v>-16.81971004921093</v>
       </c>
       <c r="F41">
-        <v>-2.185432164009276</v>
+        <v>-2.355467827312319</v>
       </c>
       <c r="G41">
-        <v>-4.518899122319043</v>
+        <v>-4.301978936403838</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.579130148965993</v>
       </c>
       <c r="E42">
-        <v>-17.38191104031519</v>
+        <v>-16.24773661119811</v>
       </c>
       <c r="F42">
-        <v>-2.312878145664785</v>
+        <v>-2.438104931048195</v>
       </c>
       <c r="G42">
-        <v>-4.43578787655564</v>
+        <v>-4.534303090713272</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.490806551225601</v>
       </c>
       <c r="E43">
-        <v>-16.33999974063039</v>
+        <v>-16.2897608499893</v>
       </c>
       <c r="F43">
-        <v>-2.958293980616797</v>
+        <v>-2.673536887332648</v>
       </c>
       <c r="G43">
-        <v>-3.902101451260811</v>
+        <v>-4.252704776597326</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.518653338108828</v>
       </c>
       <c r="E44">
-        <v>-15.37657142397253</v>
+        <v>-14.36208003440418</v>
       </c>
       <c r="F44">
-        <v>-2.629881925205114</v>
+        <v>-2.740109462026033</v>
       </c>
       <c r="G44">
-        <v>-3.546399885793818</v>
+        <v>-3.931482542921843</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.638180310747457</v>
       </c>
       <c r="E45">
-        <v>-14.90202810423475</v>
+        <v>-14.83335832438243</v>
       </c>
       <c r="F45">
-        <v>-2.591599754052138</v>
+        <v>-2.565059690833844</v>
       </c>
       <c r="G45">
-        <v>-3.974824205121981</v>
+        <v>-4.244613803299347</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.819604995883395</v>
       </c>
       <c r="E46">
-        <v>-15.68610167934482</v>
+        <v>-14.52441677063115</v>
       </c>
       <c r="F46">
-        <v>-2.780533791282649</v>
+        <v>-2.702829615430444</v>
       </c>
       <c r="G46">
-        <v>-3.925060084575656</v>
+        <v>-3.996912164959999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.041640330523739</v>
       </c>
       <c r="E47">
-        <v>-15.08421767051134</v>
+        <v>-13.4014774855271</v>
       </c>
       <c r="F47">
-        <v>-2.546999624718009</v>
+        <v>-2.788673329382557</v>
       </c>
       <c r="G47">
-        <v>-3.3299001391621</v>
+        <v>-3.917849716391124</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.282556974785048</v>
       </c>
       <c r="E48">
-        <v>-13.53768039825581</v>
+        <v>-12.91757381001547</v>
       </c>
       <c r="F48">
-        <v>-2.996167766640194</v>
+        <v>-2.913687224343447</v>
       </c>
       <c r="G48">
-        <v>-3.867867099839208</v>
+        <v>-3.795594580171378</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.522502981850946</v>
       </c>
       <c r="E49">
-        <v>-12.62097234793508</v>
+        <v>-12.62034741852202</v>
       </c>
       <c r="F49">
-        <v>-2.929508213369515</v>
+        <v>-2.918328566901332</v>
       </c>
       <c r="G49">
-        <v>-3.439571891787076</v>
+        <v>-3.91773053675171</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.753885988963625</v>
       </c>
       <c r="E50">
-        <v>-12.4462909915632</v>
+        <v>-11.69666098975548</v>
       </c>
       <c r="F50">
-        <v>-2.969128197878012</v>
+        <v>-3.337731811306125</v>
       </c>
       <c r="G50">
-        <v>-3.39076782944714</v>
+        <v>-3.481374150311454</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.971999371219729</v>
       </c>
       <c r="E51">
-        <v>-12.29038015995312</v>
+        <v>-11.61653417066376</v>
       </c>
       <c r="F51">
-        <v>-2.761705000217016</v>
+        <v>-3.227222629568254</v>
       </c>
       <c r="G51">
-        <v>-4.495145958074772</v>
+        <v>-3.425879475436651</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.172923702465575</v>
       </c>
       <c r="E52">
-        <v>-12.49864015109187</v>
+        <v>-10.58600745463424</v>
       </c>
       <c r="F52">
-        <v>-3.290816395081172</v>
+        <v>-3.25133723303115</v>
       </c>
       <c r="G52">
-        <v>-4.392184681257899</v>
+        <v>-3.655240691488437</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.361481425269131</v>
       </c>
       <c r="E53">
-        <v>-12.64993646768814</v>
+        <v>-10.1033989226888</v>
       </c>
       <c r="F53">
-        <v>-3.443457999660231</v>
+        <v>-3.218547966126138</v>
       </c>
       <c r="G53">
-        <v>-3.529684941366038</v>
+        <v>-4.283410086474066</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.542149616002261</v>
       </c>
       <c r="E54">
-        <v>-10.99046811062932</v>
+        <v>-9.325162550574618</v>
       </c>
       <c r="F54">
-        <v>-3.08462829321775</v>
+        <v>-3.33715940943079</v>
       </c>
       <c r="G54">
-        <v>-3.486230720617564</v>
+        <v>-3.206377064000814</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.71612142745095</v>
       </c>
       <c r="E55">
-        <v>-10.38310917672057</v>
+        <v>-8.863439340752548</v>
       </c>
       <c r="F55">
-        <v>-3.373000381847717</v>
+        <v>-3.273970715577841</v>
       </c>
       <c r="G55">
-        <v>-3.997104176601276</v>
+        <v>-3.433907548369383</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.889949625161734</v>
       </c>
       <c r="E56">
-        <v>-10.09472689496411</v>
+        <v>-8.605293679945298</v>
       </c>
       <c r="F56">
-        <v>-3.330115801404786</v>
+        <v>-3.391570722283676</v>
       </c>
       <c r="G56">
-        <v>-3.585672887526192</v>
+        <v>-3.179796693866006</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.067837802754517</v>
       </c>
       <c r="E57">
-        <v>-9.576189450241808</v>
+        <v>-9.231160487123395</v>
       </c>
       <c r="F57">
-        <v>-3.523365632803883</v>
+        <v>-3.471626633192429</v>
       </c>
       <c r="G57">
-        <v>-4.157903994534756</v>
+        <v>-3.886154553398141</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.250105250181829</v>
       </c>
       <c r="E58">
-        <v>-8.742918533512409</v>
+        <v>-8.299730367803733</v>
       </c>
       <c r="F58">
-        <v>-3.416811077046977</v>
+        <v>-3.602929493475373</v>
       </c>
       <c r="G58">
-        <v>-4.377197841601619</v>
+        <v>-3.722693056851087</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.441968500128256</v>
       </c>
       <c r="E59">
-        <v>-9.348760428628587</v>
+        <v>-7.926407499085397</v>
       </c>
       <c r="F59">
-        <v>-3.666876971869286</v>
+        <v>-3.749524016013996</v>
       </c>
       <c r="G59">
-        <v>-4.012991484644239</v>
+        <v>-3.885820188298675</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.642669737428969</v>
       </c>
       <c r="E60">
-        <v>-7.269045155183952</v>
+        <v>-7.42807610538532</v>
       </c>
       <c r="F60">
-        <v>-3.431430104971583</v>
+        <v>-3.360765395308368</v>
       </c>
       <c r="G60">
-        <v>-4.152898449679378</v>
+        <v>-3.473455325381517</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.845659826932797</v>
       </c>
       <c r="E61">
-        <v>-8.392455401584792</v>
+        <v>-6.646520361823516</v>
       </c>
       <c r="F61">
-        <v>-4.124705694987739</v>
+        <v>-3.614129849128625</v>
       </c>
       <c r="G61">
-        <v>-4.206069121585613</v>
+        <v>-4.086094951242425</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.05067399547227</v>
       </c>
       <c r="E62">
-        <v>-7.421478118756144</v>
+        <v>-6.144194854048674</v>
       </c>
       <c r="F62">
-        <v>-3.286031744962602</v>
+        <v>-3.220570839323774</v>
       </c>
       <c r="G62">
-        <v>-4.107279132148221</v>
+        <v>-3.935256564836612</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.251805009995158</v>
       </c>
       <c r="E63">
-        <v>-7.652099714544772</v>
+        <v>-6.313378642975239</v>
       </c>
       <c r="F63">
-        <v>-3.619660858277117</v>
+        <v>-3.531583037439654</v>
       </c>
       <c r="G63">
-        <v>-4.580793081721257</v>
+        <v>-4.128638771967599</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.439285391470645</v>
       </c>
       <c r="E64">
-        <v>-7.463484243651295</v>
+        <v>-6.204885462699472</v>
       </c>
       <c r="F64">
-        <v>-3.551646095935458</v>
+        <v>-3.568801584847436</v>
       </c>
       <c r="G64">
-        <v>-3.769017520582109</v>
+        <v>-3.9582946512444</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.610273631027236</v>
       </c>
       <c r="E65">
-        <v>-7.004754355148295</v>
+        <v>-6.559922353374835</v>
       </c>
       <c r="F65">
-        <v>-3.705616401828608</v>
+        <v>-3.593094287301934</v>
       </c>
       <c r="G65">
-        <v>-4.624042048646296</v>
+        <v>-3.970762165745295</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.756292465344778</v>
       </c>
       <c r="E66">
-        <v>-8.326982724381894</v>
+        <v>-6.595412004172949</v>
       </c>
       <c r="F66">
-        <v>-3.848569421264524</v>
+        <v>-3.351746131026687</v>
       </c>
       <c r="G66">
-        <v>-4.636754543517098</v>
+        <v>-4.12300091291422</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.864926454225213</v>
       </c>
       <c r="E67">
-        <v>-7.216379002474747</v>
+        <v>-5.449558640590094</v>
       </c>
       <c r="F67">
-        <v>-3.494371116971095</v>
+        <v>-3.623333010973727</v>
       </c>
       <c r="G67">
-        <v>-4.980018389393049</v>
+        <v>-3.966935175101898</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.929881665484167</v>
       </c>
       <c r="E68">
-        <v>-7.028777909758986</v>
+        <v>-5.972330208509568</v>
       </c>
       <c r="F68">
-        <v>-3.642591724721413</v>
+        <v>-3.874272005038587</v>
       </c>
       <c r="G68">
-        <v>-4.444451574231913</v>
+        <v>-3.102793404622558</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.940656129139184</v>
       </c>
       <c r="E69">
-        <v>-7.489409757345207</v>
+        <v>-5.619340188085672</v>
       </c>
       <c r="F69">
-        <v>-3.8797499986733</v>
+        <v>-3.826405623035221</v>
       </c>
       <c r="G69">
-        <v>-4.552593854817745</v>
+        <v>-3.350289789138472</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.888709537821069</v>
       </c>
       <c r="E70">
-        <v>-6.293475999711527</v>
+        <v>-5.80449590483729</v>
       </c>
       <c r="F70">
-        <v>-3.909402238223911</v>
+        <v>-3.879851059496442</v>
       </c>
       <c r="G70">
-        <v>-4.422337130029582</v>
+        <v>-3.567488060878976</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.777342520495361</v>
       </c>
       <c r="E71">
-        <v>-7.260255387135064</v>
+        <v>-5.513482579682369</v>
       </c>
       <c r="F71">
-        <v>-3.760494085529269</v>
+        <v>-3.661613525391898</v>
       </c>
       <c r="G71">
-        <v>-3.761221185837126</v>
+        <v>-3.717233967256829</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.60947492181834</v>
       </c>
       <c r="E72">
-        <v>-7.488128199201037</v>
+        <v>-5.28562335303842</v>
       </c>
       <c r="F72">
-        <v>-3.904408839519836</v>
+        <v>-3.991823138067657</v>
       </c>
       <c r="G72">
-        <v>-4.113956502500931</v>
+        <v>-3.69433823430723</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.390085483047958</v>
       </c>
       <c r="E73">
-        <v>-7.654739814891244</v>
+        <v>-5.640578731181646</v>
       </c>
       <c r="F73">
-        <v>-3.781981935957889</v>
+        <v>-3.997284564354314</v>
       </c>
       <c r="G73">
-        <v>-4.524262206092663</v>
+        <v>-4.023234312542743</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.129955349563606</v>
       </c>
       <c r="E74">
-        <v>-8.43454303901208</v>
+        <v>-6.474343251577881</v>
       </c>
       <c r="F74">
-        <v>-3.753095936254867</v>
+        <v>-4.036337945559296</v>
       </c>
       <c r="G74">
-        <v>-3.584378464220337</v>
+        <v>-3.60267253887035</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.834276784906298</v>
       </c>
       <c r="E75">
-        <v>-8.487983560776598</v>
+        <v>-6.616994711293505</v>
       </c>
       <c r="F75">
-        <v>-3.933093545943977</v>
+        <v>-4.105491713079805</v>
       </c>
       <c r="G75">
-        <v>-3.089100988272132</v>
+        <v>-2.122415069713867</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.508954122719179</v>
       </c>
       <c r="E76">
-        <v>-7.781922007396666</v>
+        <v>-6.959293004585292</v>
       </c>
       <c r="F76">
-        <v>-4.387762875788153</v>
+        <v>-4.166843916400747</v>
       </c>
       <c r="G76">
-        <v>-3.515035777354763</v>
+        <v>-2.124225938123848</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.165743569492515</v>
       </c>
       <c r="E77">
-        <v>-8.006267138210664</v>
+        <v>-7.335708821050868</v>
       </c>
       <c r="F77">
-        <v>-3.947401936092533</v>
+        <v>-4.344124481008675</v>
       </c>
       <c r="G77">
-        <v>-2.507583801025912</v>
+        <v>-2.100896523708604</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.811707111114469</v>
       </c>
       <c r="E78">
-        <v>-8.256741564048919</v>
+        <v>-7.033134301754365</v>
       </c>
       <c r="F78">
-        <v>-4.306500861940925</v>
+        <v>-4.26966336353843</v>
       </c>
       <c r="G78">
-        <v>-2.651029739242533</v>
+        <v>-2.220946836599195</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.456148689606162</v>
       </c>
       <c r="E79">
-        <v>-10.68197487580479</v>
+        <v>-8.276866102539005</v>
       </c>
       <c r="F79">
-        <v>-4.757182431108023</v>
+        <v>-4.417383637377458</v>
       </c>
       <c r="G79">
-        <v>-2.125109853782833</v>
+        <v>-1.287929166175318</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.115417447389187</v>
       </c>
       <c r="E80">
-        <v>-9.460500524767854</v>
+        <v>-8.525791790266638</v>
       </c>
       <c r="F80">
-        <v>-4.441335052462002</v>
+        <v>-4.758883897753374</v>
       </c>
       <c r="G80">
-        <v>-3.270525504915271</v>
+        <v>-0.9988721929593936</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.800621768645679</v>
       </c>
       <c r="E81">
-        <v>-10.07314418784355</v>
+        <v>-9.51493278234005</v>
       </c>
       <c r="F81">
-        <v>-4.897043155029289</v>
+        <v>-4.532277367778346</v>
       </c>
       <c r="G81">
-        <v>-1.99825968035458</v>
+        <v>-1.495652656582428</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.522932233714244</v>
       </c>
       <c r="E82">
-        <v>-12.49608156327754</v>
+        <v>-9.846715958986028</v>
       </c>
       <c r="F82">
-        <v>-4.666819144606237</v>
+        <v>-5.012533309960193</v>
       </c>
       <c r="G82">
-        <v>-2.065334643525753</v>
+        <v>-0.6892865268544485</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.297995310361601</v>
       </c>
       <c r="E83">
-        <v>-11.99629200094699</v>
+        <v>-11.15491058726986</v>
       </c>
       <c r="F83">
-        <v>-4.711088755346648</v>
+        <v>-5.268296715778957</v>
       </c>
       <c r="G83">
-        <v>-1.702661069153055</v>
+        <v>-0.6637324258368142</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.133398394384054</v>
       </c>
       <c r="E84">
-        <v>-12.11406402446448</v>
+        <v>-11.9346005995405</v>
       </c>
       <c r="F84">
-        <v>-5.017690725410023</v>
+        <v>-5.19139357120526</v>
       </c>
       <c r="G84">
-        <v>-1.276368741152183</v>
+        <v>-0.4576873820181148</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.034586817131284</v>
       </c>
       <c r="E85">
-        <v>-13.50881590493091</v>
+        <v>-12.78489405006473</v>
       </c>
       <c r="F85">
-        <v>-5.254192932378893</v>
+        <v>-5.457555473031366</v>
       </c>
       <c r="G85">
-        <v>-0.6797985033388972</v>
+        <v>-0.07738846319433718</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.010982558403744</v>
       </c>
       <c r="E86">
-        <v>-15.03845291218982</v>
+        <v>-13.90864846049015</v>
       </c>
       <c r="F86">
-        <v>-5.213217738799416</v>
+        <v>-5.592185885171356</v>
       </c>
       <c r="G86">
-        <v>-0.8142430682342394</v>
+        <v>0.7388761976960631</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.063105715249415</v>
       </c>
       <c r="E87">
-        <v>-16.07675501809051</v>
+        <v>-14.66669689547814</v>
       </c>
       <c r="F87">
-        <v>-5.174574399458819</v>
+        <v>-5.795733151754654</v>
       </c>
       <c r="G87">
-        <v>-0.2024376998492277</v>
+        <v>0.3573159610218231</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.189997454275551</v>
       </c>
       <c r="E88">
-        <v>-16.98491330948475</v>
+        <v>-16.77209767349428</v>
       </c>
       <c r="F88">
-        <v>-5.56619834301073</v>
+        <v>-5.993484331620563</v>
       </c>
       <c r="G88">
-        <v>-0.526712256511919</v>
+        <v>0.3803672896117684</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.397586011718951</v>
       </c>
       <c r="E89">
-        <v>-19.27727666538157</v>
+        <v>-18.13335696019999</v>
       </c>
       <c r="F89">
-        <v>-5.786872934014309</v>
+        <v>-5.865041823979485</v>
       </c>
       <c r="G89">
-        <v>-0.672031963503767</v>
+        <v>0.5905372731723997</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.683588524063832</v>
       </c>
       <c r="E90">
-        <v>-21.05092143759578</v>
+        <v>-18.89997326801049</v>
       </c>
       <c r="F90">
-        <v>-5.969088911608117</v>
+        <v>-5.933857617599651</v>
       </c>
       <c r="G90">
-        <v>-1.058233585024065</v>
+        <v>1.031518491731018</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.043789340855348</v>
       </c>
       <c r="E91">
-        <v>-22.97966191609869</v>
+        <v>-20.62598755061202</v>
       </c>
       <c r="F91">
-        <v>-5.641842369132172</v>
+        <v>-6.159126334219157</v>
       </c>
       <c r="G91">
-        <v>-0.6978608398011609</v>
+        <v>0.08916177234085697</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.478007329447554</v>
       </c>
       <c r="E92">
-        <v>-24.41116689161138</v>
+        <v>-23.6811044259908</v>
       </c>
       <c r="F92">
-        <v>-6.010760762173349</v>
+        <v>-6.464445163175596</v>
       </c>
       <c r="G92">
-        <v>-0.7029822537504133</v>
+        <v>0.2327037163781164</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.972403194241977</v>
       </c>
       <c r="E93">
-        <v>-26.65666959847683</v>
+        <v>-24.94245199066528</v>
       </c>
       <c r="F93">
-        <v>-5.92582659562951</v>
+        <v>-6.404060907164824</v>
       </c>
       <c r="G93">
-        <v>-1.33570695939808</v>
+        <v>-0.07003574155161588</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.505616569645545</v>
       </c>
       <c r="E94">
-        <v>-28.5395683346001</v>
+        <v>-27.4020111353993</v>
       </c>
       <c r="F94">
-        <v>-6.292070190327047</v>
+        <v>-6.756010608143355</v>
       </c>
       <c r="G94">
-        <v>-1.637105646384407</v>
+        <v>-0.1580068681666691</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.059613926273512</v>
       </c>
       <c r="E95">
-        <v>-30.06435534619679</v>
+        <v>-29.85707350544369</v>
       </c>
       <c r="F95">
-        <v>-6.448493706283587</v>
+        <v>-6.732542959622045</v>
       </c>
       <c r="G95">
-        <v>-1.966110972622717</v>
+        <v>-0.6908623465311415</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.601345725775193</v>
       </c>
       <c r="E96">
-        <v>-32.43582887877061</v>
+        <v>-31.55076354057848</v>
       </c>
       <c r="F96">
-        <v>-6.413849310580005</v>
+        <v>-6.77773992766989</v>
       </c>
       <c r="G96">
-        <v>-2.562336913699919</v>
+        <v>-1.020195416777839</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.100204944018287</v>
       </c>
       <c r="E97">
-        <v>-35.40630178223501</v>
+        <v>-34.01079364660929</v>
       </c>
       <c r="F97">
-        <v>-6.544375990606526</v>
+        <v>-7.138753624769852</v>
       </c>
       <c r="G97">
-        <v>-2.587682450348579</v>
+        <v>-1.154385069666658</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.527177150107857</v>
       </c>
       <c r="E98">
-        <v>-37.42248709382604</v>
+        <v>-36.09435359448644</v>
       </c>
       <c r="F98">
-        <v>-6.518045504341141</v>
+        <v>-7.018999034449337</v>
       </c>
       <c r="G98">
-        <v>-3.389334363228636</v>
+        <v>-2.295175888680734</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.85982507221075</v>
       </c>
       <c r="E99">
-        <v>-40.25411924845228</v>
+        <v>-39.66872341348073</v>
       </c>
       <c r="F99">
-        <v>-6.830287828050178</v>
+        <v>-7.209550044850112</v>
       </c>
       <c r="G99">
-        <v>-3.405148839269734</v>
+        <v>-3.070307021245689</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.063862180209318</v>
       </c>
       <c r="E100">
-        <v>-42.89197347181629</v>
+        <v>-41.70375849812869</v>
       </c>
       <c r="F100">
-        <v>-6.671783453177805</v>
+        <v>-6.941726023830289</v>
       </c>
       <c r="G100">
-        <v>-4.3808295100582</v>
+        <v>-3.657236950448617</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.148531672598942</v>
       </c>
       <c r="E101">
-        <v>-44.87869653151341</v>
+        <v>-44.5380964159745</v>
       </c>
       <c r="F101">
-        <v>-6.777125279057013</v>
+        <v>-7.199040547610795</v>
       </c>
       <c r="G101">
-        <v>-5.333462162802259</v>
+        <v>-4.019086198982037</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.075253237085258</v>
       </c>
       <c r="E102">
-        <v>-47.54752551708989</v>
+        <v>-46.36759765083632</v>
       </c>
       <c r="F102">
-        <v>-6.718996253300364</v>
+        <v>-7.22511962436943</v>
       </c>
       <c r="G102">
-        <v>-5.882936579773872</v>
+        <v>-4.831940997966988</v>
       </c>
     </row>
   </sheetData>
